--- a/output/laminas_comunales/comunal_s_isapre_a_2022_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2022_la_araucania.xlsx
@@ -384,457 +384,457 @@
         </is>
       </c>
       <c r="C2">
-        <v>48116</v>
+        <v>15.86421320215365</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C3">
-        <v>5811</v>
+        <v>9.399865138233311</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C4">
-        <v>4364</v>
+        <v>7.865031671268475</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C5">
-        <v>3549</v>
+        <v>7.42568360870527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C6">
-        <v>3485</v>
+        <v>5.875299760191846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C7">
-        <v>2205</v>
+        <v>4.531260684247715</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C8">
-        <v>1988</v>
+        <v>4.514087690221485</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C9">
-        <v>1498</v>
+        <v>4.49234980691206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C10">
-        <v>1195</v>
+        <v>4.355509738227606</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C11">
-        <v>1091</v>
+        <v>4.275579679093463</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C12">
-        <v>949</v>
+        <v>4.193571027512633</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C13">
-        <v>919</v>
+        <v>3.951219512195122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C14">
-        <v>917</v>
+        <v>3.587630424920611</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C15">
-        <v>898</v>
+        <v>3.541499672083364</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C16">
-        <v>845</v>
+        <v>3.48741418764302</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C17">
-        <v>670</v>
+        <v>3.409803184154444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C18">
-        <v>612</v>
+        <v>3.313938780672907</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C19">
-        <v>544</v>
+        <v>3.140680170971939</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C20">
-        <v>486</v>
+        <v>3.129539152251419</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C21">
-        <v>486</v>
+        <v>3.110343125154283</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C22">
-        <v>381</v>
+        <v>2.96620537777657</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C23">
-        <v>378</v>
+        <v>2.929911911145155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C24">
-        <v>349</v>
+        <v>2.744251048151442</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C25">
-        <v>329</v>
+        <v>2.496181215304944</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C26">
-        <v>291</v>
+        <v>2.431235191099207</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C27">
-        <v>256</v>
+        <v>2.264436643953472</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C28">
-        <v>237</v>
+        <v>2.255542739971806</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="C29">
-        <v>236</v>
+        <v>2.156392942714006</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C30">
-        <v>216</v>
+        <v>2.10077967080566</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C31">
-        <v>198</v>
+        <v>2.06631142687981</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C32">
-        <v>176</v>
+        <v>1.823621598518308</v>
       </c>
     </row>
     <row r="33">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>138</v>
+        <v>1.46325946347153</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
